--- a/artfynd/A 15647-2025 artfynd.xlsx
+++ b/artfynd/A 15647-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124341141</v>
+        <v>124341140</v>
       </c>
       <c r="B2" t="n">
         <v>91030</v>
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>466159</v>
+        <v>466174</v>
       </c>
       <c r="R2" t="n">
         <v>7031246</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124341140</v>
+        <v>124341134</v>
       </c>
       <c r="B4" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>466174</v>
+        <v>466192</v>
       </c>
       <c r="R4" t="n">
-        <v>7031246</v>
+        <v>7031517</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -955,6 +955,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-04-22</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -981,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124341134</v>
+        <v>124341141</v>
       </c>
       <c r="B5" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +1002,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>466192</v>
+        <v>466159</v>
       </c>
       <c r="R5" t="n">
-        <v>7031517</v>
+        <v>7031246</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1057,11 +1062,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-04-22</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 15647-2025 artfynd.xlsx
+++ b/artfynd/A 15647-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124341140</v>
+        <v>124341134</v>
       </c>
       <c r="B2" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>466174</v>
+        <v>466192</v>
       </c>
       <c r="R2" t="n">
-        <v>7031246</v>
+        <v>7031517</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-04-22</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -879,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124341134</v>
+        <v>124341140</v>
       </c>
       <c r="B4" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>466192</v>
+        <v>466174</v>
       </c>
       <c r="R4" t="n">
-        <v>7031517</v>
+        <v>7031246</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -955,11 +960,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-04-22</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 15647-2025 artfynd.xlsx
+++ b/artfynd/A 15647-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124341134</v>
+        <v>124341127</v>
       </c>
       <c r="B2" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>466192</v>
+        <v>466130</v>
       </c>
       <c r="R2" t="n">
-        <v>7031517</v>
+        <v>7031262</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-04-22</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124341127</v>
+        <v>124341134</v>
       </c>
       <c r="B3" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>466130</v>
+        <v>466192</v>
       </c>
       <c r="R3" t="n">
-        <v>7031262</v>
+        <v>7031517</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,6 +853,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-04-22</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,7 +884,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124341140</v>
+        <v>124341141</v>
       </c>
       <c r="B4" t="n">
         <v>91030</v>
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>466174</v>
+        <v>466159</v>
       </c>
       <c r="R4" t="n">
         <v>7031246</v>
@@ -986,7 +986,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124341141</v>
+        <v>124341140</v>
       </c>
       <c r="B5" t="n">
         <v>91030</v>
@@ -1026,7 +1026,7 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>466159</v>
+        <v>466174</v>
       </c>
       <c r="R5" t="n">
         <v>7031246</v>

--- a/artfynd/A 15647-2025 artfynd.xlsx
+++ b/artfynd/A 15647-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124341127</v>
+        <v>124341134</v>
       </c>
       <c r="B2" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>466130</v>
+        <v>466192</v>
       </c>
       <c r="R2" t="n">
-        <v>7031262</v>
+        <v>7031517</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-04-22</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124341134</v>
+        <v>124341127</v>
       </c>
       <c r="B3" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>466192</v>
+        <v>466130</v>
       </c>
       <c r="R3" t="n">
-        <v>7031517</v>
+        <v>7031262</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,11 +858,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-04-22</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 15647-2025 artfynd.xlsx
+++ b/artfynd/A 15647-2025 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124341127</v>
+        <v>124341140</v>
       </c>
       <c r="B3" t="n">
-        <v>91012</v>
+        <v>91030</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>466130</v>
+        <v>466174</v>
       </c>
       <c r="R3" t="n">
-        <v>7031262</v>
+        <v>7031246</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -986,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124341140</v>
+        <v>124341127</v>
       </c>
       <c r="B5" t="n">
-        <v>91030</v>
+        <v>91012</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,21 +1002,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>466174</v>
+        <v>466130</v>
       </c>
       <c r="R5" t="n">
-        <v>7031246</v>
+        <v>7031262</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 15647-2025 artfynd.xlsx
+++ b/artfynd/A 15647-2025 artfynd.xlsx
@@ -682,7 +682,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">

--- a/artfynd/A 15647-2025 artfynd.xlsx
+++ b/artfynd/A 15647-2025 artfynd.xlsx
@@ -675,14 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124341134</v>
+        <v>124341140</v>
       </c>
       <c r="B2" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>466192</v>
+        <v>466174</v>
       </c>
       <c r="R2" t="n">
-        <v>7031517</v>
+        <v>7031246</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-04-22</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124341140</v>
+        <v>124341127</v>
       </c>
       <c r="B3" t="n">
-        <v>91030</v>
+        <v>91012</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>466174</v>
+        <v>466130</v>
       </c>
       <c r="R3" t="n">
-        <v>7031246</v>
+        <v>7031262</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -986,14 +981,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124341127</v>
+        <v>124341134</v>
       </c>
       <c r="B5" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1002,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>466130</v>
+        <v>466192</v>
       </c>
       <c r="R5" t="n">
-        <v>7031262</v>
+        <v>7031517</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1062,6 +1057,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-04-22</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 15647-2025 artfynd.xlsx
+++ b/artfynd/A 15647-2025 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124341127</v>
+        <v>124341141</v>
       </c>
       <c r="B3" t="n">
-        <v>91012</v>
+        <v>91030</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>466130</v>
+        <v>466159</v>
       </c>
       <c r="R3" t="n">
-        <v>7031262</v>
+        <v>7031246</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124341141</v>
+        <v>124341127</v>
       </c>
       <c r="B4" t="n">
-        <v>91030</v>
+        <v>91012</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>466159</v>
+        <v>466130</v>
       </c>
       <c r="R4" t="n">
-        <v>7031246</v>
+        <v>7031262</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 15647-2025 artfynd.xlsx
+++ b/artfynd/A 15647-2025 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124341141</v>
+        <v>124341127</v>
       </c>
       <c r="B3" t="n">
-        <v>91030</v>
+        <v>91012</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>466159</v>
+        <v>466130</v>
       </c>
       <c r="R3" t="n">
-        <v>7031246</v>
+        <v>7031262</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124341127</v>
+        <v>124341141</v>
       </c>
       <c r="B4" t="n">
-        <v>91012</v>
+        <v>91030</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>466130</v>
+        <v>466159</v>
       </c>
       <c r="R4" t="n">
-        <v>7031262</v>
+        <v>7031246</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 15647-2025 artfynd.xlsx
+++ b/artfynd/A 15647-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124341140</v>
+        <v>124341127</v>
       </c>
       <c r="B2" t="n">
-        <v>91030</v>
+        <v>91012</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>466174</v>
+        <v>466130</v>
       </c>
       <c r="R2" t="n">
-        <v>7031246</v>
+        <v>7031262</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124341127</v>
+        <v>124341140</v>
       </c>
       <c r="B3" t="n">
-        <v>91012</v>
+        <v>91030</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>466130</v>
+        <v>466174</v>
       </c>
       <c r="R3" t="n">
-        <v>7031262</v>
+        <v>7031246</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 15647-2025 artfynd.xlsx
+++ b/artfynd/A 15647-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124341127</v>
+        <v>124341140</v>
       </c>
       <c r="B2" t="n">
-        <v>91012</v>
+        <v>91030</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>466130</v>
+        <v>466174</v>
       </c>
       <c r="R2" t="n">
-        <v>7031262</v>
+        <v>7031246</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124341140</v>
+        <v>124341127</v>
       </c>
       <c r="B3" t="n">
-        <v>91030</v>
+        <v>91012</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>466174</v>
+        <v>466130</v>
       </c>
       <c r="R3" t="n">
-        <v>7031246</v>
+        <v>7031262</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 15647-2025 artfynd.xlsx
+++ b/artfynd/A 15647-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124341140</v>
+        <v>124341127</v>
       </c>
       <c r="B2" t="n">
-        <v>91030</v>
+        <v>91012</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>466174</v>
+        <v>466130</v>
       </c>
       <c r="R2" t="n">
-        <v>7031246</v>
+        <v>7031262</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124341127</v>
+        <v>124341141</v>
       </c>
       <c r="B3" t="n">
-        <v>91012</v>
+        <v>91030</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>466130</v>
+        <v>466159</v>
       </c>
       <c r="R3" t="n">
-        <v>7031262</v>
+        <v>7031246</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124341141</v>
+        <v>124341140</v>
       </c>
       <c r="B4" t="n">
         <v>91030</v>
@@ -919,7 +919,7 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>466159</v>
+        <v>466174</v>
       </c>
       <c r="R4" t="n">
         <v>7031246</v>

--- a/artfynd/A 15647-2025 artfynd.xlsx
+++ b/artfynd/A 15647-2025 artfynd.xlsx
@@ -984,7 +984,7 @@
         <v>124341134</v>
       </c>
       <c r="B5" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
